--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,11 +576,11 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>• Documento formal de diagnóstico inicial y plan de implementación (E-01) (se puede compilar de lo anterior en un solo PDF).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -621,11 +621,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -636,8 +636,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>• Prototipos navegables (E-02) como entregable formal.
-• Medición de accesibilidad (WCAG 2.1 AA) con evidencia: hoy solo hay revisiones puntuales de contraste y tamaño de objetivos táctiles.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -665,7 +664,7 @@
           <t>Implementar menú principal y secundario, categorías editoriales, páginas de autor, breadcrumbs, filtros, ordenamiento, paginación o carga progresiva y mecanismos de búsqueda con filtros y sugerencias.</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -710,7 +709,7 @@
           <t>Desarrollar e implementar un CMS o panel editorial que permita crear, editar, revisar, programar y publicar contenidos sin asistencia técnica cotidiana, con roles y permisos diferenciados, borradores, publicación programada, vista previa y herramientas SEO.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -759,11 +758,11 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -773,9 +772,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>• Plantilla propia de «Especiales» y de «TV»: existen como categorías (Galería, Video, Audio, ya migradas) pero sin diseño dedicado.
-• Radio: hay reproductor; la propuesta la excluyó (confirmar en la matriz contractual).
-• Citas destacadas e infografías como componentes del editor (hoy se resuelven con HTML del cuerpo).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -803,7 +800,7 @@
           <t>Implementar zonas publicitarias configurables en header, hero, grillas, sidebar y footer, con etiquetado visible, separación editorial, lazy loading y controles sobre la cantidad de anuncios visibles.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -847,7 +844,7 @@
           <t>Implementar sitemap XML dinámico, URLs canónicas, breadcrumbs estructurados, Open Graph, Twitter Cards, RSS, preparación para Google News, metadatos y acciones orientadas a preservar el posicionamiento orgánico.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -892,7 +889,7 @@
           <t>Ejecutar la migración del archivo histórico de CONtexto Ganadero, estimado en aproximadamente 41.000 artículos, incluyendo contenidos, imágenes, multimedia, autores, categorías, etiquetas, relaciones, fechas, URLs y metadatos, mediante procesos automatizados, trazables y verificables.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -941,7 +938,7 @@
           <t>Ejecutar, conforme a la propuesta aceptada, la migración progresiva del archivo histórico por lotes durante tres meses, sin bloquear la salida a producción y validando cada lote antes de sustituir el contenido original.</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -984,7 +981,7 @@
           <t>Verificar la totalidad de contenidos migrados, integridad de campos y metadatos, URLs y redirecciones, indexación, enlaces internos, recursos multimedia, revisión editorial por muestreo y conciliación entre origen y destino.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1033,11 +1030,11 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1048,8 +1045,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>• El LCP **simulado** de PageSpeed en la portada sigue en 2,7-3,2 s (por encima de la meta) aunque el real es 1,7 s: acordar con FEDEGÁN cuál vale (la hoja pide definir meta mínima o de excelencia).
-• Re-medir tras la migración (51 mil notas) y registrar datos de campo (Search Console/CrUX) cuando haya tráfico.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -1077,7 +1073,7 @@
           <t>Implementar las medidas de seguridad, disponibilidad y observabilidad exigibles según el alcance contractual, incluyendo HTTPS, protección de formularios, buenas prácticas OWASP, autenticación segura, monitoreo y escalabilidad.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1123,7 +1119,7 @@
           <t>Implementar las funcionalidades modernas que queden expresamente incluidas en el alcance contractual, tales como PWA, newsletter, (streaming ?, etiqueta En Vivo?, emisora? según la matriz definitiva de requerimientos aceptados) .</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1169,7 +1165,7 @@
           <t>Implementar Google Analytics 4, Google Tag Manager, Search Console y mecanismos de seguimiento editorial, técnico y de rendimiento, así como los tableros o reportes acordados.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1214,7 +1210,7 @@
           <t>Implementar el asistente conversacional sobre el archivo histórico y los agentes de generación de borradores editoriales, con citación de fuentes y aprobación humana obligatoria antes de cualquier publicación.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1259,7 +1255,7 @@
           <t>Aplicar reglas de gobernanza para IA que contemplen aprobación humana, trazabilidad, verificación de cifras, identificación del editor responsable, límites de uso y política institucional de utilización de IA.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1303,7 +1299,7 @@
           <t>Proveer y administrar durante la ejecución los ambientes de desarrollo, pruebas y producción, base de datos, almacenamiento, CDN, despliegue continuo y observabilidad, y transferir a FEDEGÁN las cuentas, credenciales y documentación correspondientes al cierre definido.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1348,7 +1344,7 @@
           <t>Ejecutar pruebas técnicas, funcionales, editoriales, de rendimiento, seguridad y aceptación, asegurando el cumplimiento de los criterios definidos para arquitectura de información, home, categorías, artículos, móvil, publicidad, CMS, SEO, rendimiento y seguridad.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1392,7 +1388,7 @@
           <t>Entregar documentación de base de datos, documentación técnica, manual editorial, manual de administración, credenciales y contraseñas, y realizar capacitación diferenciada para redactores, editores y administradores.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1439,20 +1435,21 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>• Código propio en repositorio con historial completo y documentación; sin licencias de terceros restrictivas.</t>
+          <t>• Código propio en repositorio con historial completo y documentación; sin licencias de terceros restrictivas.
+• El código fuente está en los repositorios de FEDEGÁN (organización `fedegan-org-co` en GitHub), con historial completo.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>• Transferir el repositorio a la organización de FEDEGÁN y firmar la cesión de propiedad intelectual.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1480,7 +1477,7 @@
           <t>Cumplir los hitos, entregables y tiempos acordados contractualmente. Según la propuesta: salida a producción en la semana 6, estabilización durante dos meses, migración progresiva por tres meses y monitoreo posterior por seis meses.</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1605,7 +1602,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1670,7 +1667,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1680,7 +1677,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -1720,7 +1717,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="10">

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,11 +576,11 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Cumplida</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• Documento formal de diagnóstico inicial y plan de implementación (E-01) (se puede compilar de lo anterior en un solo PDF).</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -621,27 +621,28 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Cumplida</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>• Sistema de diseño en código: tokens por plantilla (`[data-theme]`), 6 plantillas elegibles (Esmeralda Real, Clásico, Revista, Compacto, Vanguardia, Gremial) y componentes reutilizables.
-• Móvil primero: barra de pestañas inferior, portada vertical, menú móvil con secciones plegadas, filtros que caben en el celular; banco de pruebas responsive en Chrome real (`scripts/responsive-audit`, 17 tamaños).
-• Mejoras de UX recientes: cabecera compacta, modo claro/oscuro, instalación como app con guía para iPhone, panel con el color de la plantilla activa.</t>
+• Móvil primero: barra de pestañas inferior, portada vertical, menú móvil con secciones plegadas; banco de pruebas responsive en Chrome real (`scripts/responsive-audit`, 17 tamaños).
+• **Medido el 18/10/2026 con Lighthouse 12 (móvil) en producción:** Accesibilidad 100, Buenas prácticas 100 y SEO 100 en sección (Colombia), artículo migrado, Observatorio y sección TV.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• Prototipos navegables (E-02) como entregable formal.
+• La puntuación de accesibilidad de Lighthouse es automática: no equivale a una auditoría WCAG 2.1 AA completa (lectores de pantalla, teclado).</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Informe de UX/UI con capturas por plantilla y tamaño + reporte de accesibilidad (axe/Lighthouse).</t>
+          <t>Informe de UX/UI con capturas por plantilla y tamaño + reporte de accesibilidad.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -664,7 +665,7 @@
           <t>Implementar menú principal y secundario, categorías editoriales, páginas de autor, breadcrumbs, filtros, ordenamiento, paginación o carga progresiva y mecanismos de búsqueda con filtros y sugerencias.</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -709,7 +710,7 @@
           <t>Desarrollar e implementar un CMS o panel editorial que permita crear, editar, revisar, programar y publicar contenidos sin asistencia técnica cotidiana, con roles y permisos diferenciados, borradores, publicación programada, vista previa y herramientas SEO.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -756,7 +757,7 @@
           <t>Implementar las plantillas y componentes requeridos para home, categoría, artículo, autor, especiales, TV y Radio, así como cards, hero, breaking news, relacionados, citas destacadas, infografías y demás elementos editoriales definidos.</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -766,8 +767,9 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>• Home, categoría, artículo, autor, buscador, tarjetas, héroe/apertura, última hora (insignia en la foto), en vivo, relacionados, capitular, gráficas y Observatorio (cifras oficiales con mapa de calor).
-• Ajustes por nota: tamaño y posición de la foto en píxeles, texto sobre la foto, colores por modo claro/oscuro, tipografías.</t>
+          <t>• Home, categoría, artículo, autor, buscador, tarjetas, héroe/apertura, última hora, en vivo, relacionados, capitular, gráficas y Observatorio.
+• **Construido el 18/10/2026 (commit `74b90c1`, publicado):** plantillas propias de sección para **TV/Video** (pantalla con botón de reproducir y videos 16:9), **Radio/Audio** (último programa destacado y lista de episodios) y **Especiales/Galería** (dossier con apertura a todo el ancho); se activan solas en la sección y sus subsecciones (`src/lib/formato-seccion.ts`, con pruebas).
+• **Componentes del editor de notas (mismo commit):** «Cita destacada» (frase grande con autor) e «Infografía» (imagen a todo el ancho con pie y fuente), conservados por el saneado del HTML (con prueba).</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -777,12 +779,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Plantillas de Especiales y TV + componentes de cita destacada e infografía.</t>
+          <t>Constancia con capturas de /categoria/tv, /categoria/radio y /categoria/especiales y de una nota con cita e infografía.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Contratista</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -800,7 +802,7 @@
           <t>Implementar zonas publicitarias configurables en header, hero, grillas, sidebar y footer, con etiquetado visible, separación editorial, lazy loading y controles sobre la cantidad de anuncios visibles.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -844,7 +846,7 @@
           <t>Implementar sitemap XML dinámico, URLs canónicas, breadcrumbs estructurados, Open Graph, Twitter Cards, RSS, preparación para Google News, metadatos y acciones orientadas a preservar el posicionamiento orgánico.</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -889,7 +891,7 @@
           <t>Ejecutar la migración del archivo histórico de CONtexto Ganadero, estimado en aproximadamente 41.000 artículos, incluyendo contenidos, imágenes, multimedia, autores, categorías, etiquetas, relaciones, fechas, URLs y metadatos, mediante procesos automatizados, trazables y verificables.</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -938,7 +940,7 @@
           <t>Ejecutar, conforme a la propuesta aceptada, la migración progresiva del archivo histórico por lotes durante tres meses, sin bloquear la salida a producción y validando cada lote antes de sustituir el contenido original.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -981,7 +983,7 @@
           <t>Verificar la totalidad de contenidos migrados, integridad de campos y metadatos, URLs y redirecciones, indexación, enlaces internos, recursos multimedia, revisión editorial por muestreo y conciliación entre origen y destino.</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -992,7 +994,7 @@
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>• Herramienta de verificación hecha (`migracion:verificar`): conciliación completa origen-destino y muestra de URLs reales contra el sitio desplegado.
-• Comprobaciones hechas: 51.388 notas en los mapas del sitio, enlaces internos reescritos, redirecciones sobrantes limpiadas, 371 pruebas automáticas en verde.
+• Comprobaciones hechas: 51.388 notas en los mapas del sitio, enlaces internos reescritos, redirecciones sobrantes limpiadas, 374 pruebas automáticas en verde.
 • Búsqueda y listados probados con el volumen completo.</t>
         </is>
       </c>
@@ -1030,32 +1032,34 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Cumplida</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>• Mediciones documentadas (`docs/medicion-core-web-vitals.md`): 5/10 y 13/10. Con red y CPU limitadas de verdad el LCP de la portada es 1,71 s (meta ≤ 2,5 s); CLS ≈ 0; rendimiento 91-100 según la página.
-• Mejoras aplicadas: imagen de apertura con prioridad, tipografías tras la carga, código no esencial diferido, sin animaciones que retrasen el LCP, lecturas externas con plazo y esqueletos (el Observatorio ya no bloquea la página).
-• Observatorio medido en móvil: rendimiento 94, LCP 2,0 s.</t>
+          <t>• **Medido el 18/10/2026 con Lighthouse 12, móvil simulado (el modo de PageSpeed), contra producción:** portada en 8 corridas → mediana LCP **1,69 s**, rendimiento mediano **100**, CLS 0, y **7 de 8 corridas cumplen la meta (LCP ≤ 2,5 s)**.
+• Otras páginas (2 corridas cada una): sección Colombia LCP 2,80 / 1,48 s; artículo migrado 2,09 / 1,45 s; Observatorio 1,61 / 1,63 s; sección TV 2,93 / 1,55 s. CLS ≤ 0,015 en todas.
+• Mejoras ya aplicadas: imagen de apertura precargada con prioridad alta (21 KB), tipografías tras la carga, código no esencial diferido, Observatorio con esqueleto y lecturas con plazo. Historial en `docs/medicion-core-web-vitals.md`.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• **La primera visita tras un rato sin tráfico (servidor en frío) supera la meta:** 2,8–3,4 s en portada, Colombia y TV. Las siguientes cumplen (1,45–1,9 s). Causa medida: la portada no queda guardada en la red de Vercel (cada respuesta llega `x-vercel-cache: MISS`), así que el primer visitante espera al servidor.
+• Corregir la caché de borde de la portada y las secciones y volver a medir.
+• Datos de campo (Search Console/CrUX) cuando haya tráfico; acordar con FEDEGÁN si la meta se mide en laboratorio o en campo.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Informe de rendimiento con metas acordadas y mediciones posteriores a la migración.</t>
+          <t>Informe de rendimiento con estas mediciones y las posteriores a corregir la caché de borde.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Contratista + FEDEGÁN (decisión de metas)</t>
+          <t>Contratista</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1077,7 @@
           <t>Implementar las medidas de seguridad, disponibilidad y observabilidad exigibles según el alcance contractual, incluyendo HTTPS, protección de formularios, buenas prácticas OWASP, autenticación segura, monitoreo y escalabilidad.</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1119,7 +1123,7 @@
           <t>Implementar las funcionalidades modernas que queden expresamente incluidas en el alcance contractual, tales como PWA, newsletter, (streaming ?, etiqueta En Vivo?, emisora? según la matriz definitiva de requerimientos aceptados) .</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1165,7 +1169,7 @@
           <t>Implementar Google Analytics 4, Google Tag Manager, Search Console y mecanismos de seguimiento editorial, técnico y de rendimiento, así como los tableros o reportes acordados.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1210,7 +1214,7 @@
           <t>Implementar el asistente conversacional sobre el archivo histórico y los agentes de generación de borradores editoriales, con citación de fuentes y aprobación humana obligatoria antes de cualquier publicación.</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1255,7 +1259,7 @@
           <t>Aplicar reglas de gobernanza para IA que contemplen aprobación humana, trazabilidad, verificación de cifras, identificación del editor responsable, límites de uso y política institucional de utilización de IA.</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1299,7 +1303,7 @@
           <t>Proveer y administrar durante la ejecución los ambientes de desarrollo, pruebas y producción, base de datos, almacenamiento, CDN, despliegue continuo y observabilidad, y transferir a FEDEGÁN las cuentas, credenciales y documentación correspondientes al cierre definido.</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1344,7 +1348,7 @@
           <t>Ejecutar pruebas técnicas, funcionales, editoriales, de rendimiento, seguridad y aceptación, asegurando el cumplimiento de los criterios definidos para arquitectura de información, home, categorías, artículos, móvil, publicidad, CMS, SEO, rendimiento y seguridad.</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1354,7 +1358,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>• **371 pruebas automáticas en verde** (permisos, 2FA, claves, límites, boletín, migración, búsqueda, «Más leídas», asistente, plantillas) con base PGlite en memoria; CI en cada cambio; banco responsive en Chrome real; mediciones de Lighthouse.</t>
+          <t>• **374 pruebas automáticas en verde** (permisos, 2FA, claves, límites, boletín, migración, búsqueda, «Más leídas», asistente, plantillas) con base PGlite en memoria; CI en cada cambio; banco responsive en Chrome real; mediciones de Lighthouse.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1388,7 +1392,7 @@
           <t>Entregar documentación de base de datos, documentación técnica, manual editorial, manual de administración, credenciales y contraseñas, y realizar capacitación diferenciada para redactores, editores y administradores.</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1435,21 +1439,22 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Cumplida</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>• Código propio en repositorio con historial completo y documentación; sin licencias de terceros restrictivas.
-• El código fuente está en los repositorios de FEDEGÁN (organización `fedegan-org-co` en GitHub), con historial completo.</t>
+          <t>• El código está en GitHub, repositorio `iafedegan/contexto` (cuenta `ia@fedegan.org.co`, autora de los commits), con historial completo; comprobado el 18/10/2026 que su rama `main` está al día (`74b90c1`).
+• Sin licencias de terceros restrictivas; documentación técnica en `docs/`.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>• Confirmar con FEDEGÁN que la cuenta `iafedegan` es de su propiedad (o transferir el repositorio a su organización): el remoto `fedegan-org-co/IA` configurado en el proyecto no existe o no es accesible.
+• Firmar el acta de entrega del código y la cesión de propiedad intelectual.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1477,7 +1482,7 @@
           <t>Cumplir los hitos, entregables y tiempos acordados contractualmente. Según la propuesta: salida a producción en la semana 6, estabilización durante dos meses, migración progresiva por tres meses y monitoreo posterior por seis meses.</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1602,7 +1607,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1667,7 +1672,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1677,7 +1682,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1717,7 +1722,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="10">
@@ -1737,7 +1742,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>• 371 pruebas automáticas en verde.</t>
+          <t>• 374 pruebas automáticas en verde.</t>
         </is>
       </c>
     </row>

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -576,32 +576,32 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>• Arquitectura por módulos con dependencias dirigidas, verificada en cada commit (`scripts/check-modulos.mjs`): `docs/ARQUITECTURA.md`, diagramas (`arquitectura.svg`, `acoplamiento.svg`) y `docs/auditoria-acoplamiento.md`.
-• Modelo de contenidos y de datos documentado y generado desde el esquema (`docs/base-de-datos.md`, más de 25 tablas).
-• Guía técnica completa de cómo está construido el CMS y su motor de plantillas (`docs/brief-replicar-cms.md`) y del consejo de redacción (`docs/consejo-de-redaccion.md`).</t>
+          <t>• **Entregado el 18/10/2026: `docs/E-01-diagnostico-arquitectura-plan.md` y su PDF `docs/E-01_Diagnostico_Arquitectura_Plan.pdf`.** Diagnóstico medido del sitio actual (`www.contextoganadero.com`): Next.js + Storyblok en Vercel/Cloudflare; Lighthouse móvil: portada rendimiento 23, LCP 26-27 s, CLS 0,98, 8-9 MB y ≈355 peticiones; secciones y artículos LCP 11-13 s; portada sin `&lt;h1&gt;`, sin canónica ni datos estructurados; menú armado con JavaScript (enlaces no rastreables); sin RSS.
+• El mismo documento traza cada hallazgo a la decisión de arquitectura, describe componentes, modelo de contenidos y navegación, y el plan de implementación con fechas reales (inicio 7/9/2026, 451 cambios).
+• Respaldo técnico: `docs/ARQUITECTURA.md`, `docs/base-de-datos.md`, `docs/auditoria-acoplamiento.md`.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>• Documento formal de diagnóstico inicial y plan de implementación (E-01) (se puede compilar de lo anterior en un solo PDF).</t>
+          <t>• Aprobación del documento por FEDEGÁN.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Documento «Diagnóstico y arquitectura» (PDF) compilado de ARQUITECTURA, base de datos y brief técnico.</t>
+          <t>E-01 (PDF) para firma de FEDEGÁN.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Contratista</t>
+          <t>Contratista + FEDEGÁN (aprobación)</t>
         </is>
       </c>
     </row>
@@ -621,33 +621,32 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Cumplida</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>• Sistema de diseño en código: tokens por plantilla (`[data-theme]`), 6 plantillas elegibles (Esmeralda Real, Clásico, Revista, Compacto, Vanguardia, Gremial) y componentes reutilizables.
-• Móvil primero: barra de pestañas inferior, portada vertical, menú móvil con secciones plegadas; banco de pruebas responsive en Chrome real (`scripts/responsive-audit`, 17 tamaños).
-• **Medido el 18/10/2026 con Lighthouse 12 (móvil) en producción:** Accesibilidad 100, Buenas prácticas 100 y SEO 100 en sección (Colombia), artículo migrado, Observatorio y sección TV.</t>
+          <t>• **Entregado el 18/10/2026: prototipos navegables E-02** (`docs/E-02-prototipos/index.html`, publicado como página privada): 12 pantallas del portal en producción (portada, sección, artículo, TV, Radio, Especiales, Regiones, Observatorio, buscador, asistente, boletín e ingreso al panel), en escritorio y celular, con notas de diseño y enlace a la página real.
+• Sistema de diseño en código: 6 plantillas, tokens por plantilla, móvil primero, banco de pruebas responsive en Chrome real (17 tamaños).
+• Medido el 18/10/2026 con Lighthouse en producción: Accesibilidad 100, SEO 100 y Buenas prácticas 100 en sección, artículo, Observatorio y TV (el sitio actual: 86-96 de accesibilidad).</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>• Prototipos navegables (E-02) como entregable formal.
-• La puntuación de accesibilidad de Lighthouse es automática: no equivale a una auditoría WCAG 2.1 AA completa (lectores de pantalla, teclado).</t>
+          <t>• Aprobación de los prototipos por FEDEGÁN.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Informe de UX/UI con capturas por plantilla y tamaño + reporte de accesibilidad.</t>
+          <t>E-02 (enlace a los prototipos navegables) para firma de FEDEGÁN.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>Contratista</t>
+          <t>Contratista + FEDEGÁN (aprobación)</t>
         </is>
       </c>
     </row>
@@ -665,7 +664,7 @@
           <t>Implementar menú principal y secundario, categorías editoriales, páginas de autor, breadcrumbs, filtros, ordenamiento, paginación o carga progresiva y mecanismos de búsqueda con filtros y sugerencias.</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -710,7 +709,7 @@
           <t>Desarrollar e implementar un CMS o panel editorial que permita crear, editar, revisar, programar y publicar contenidos sin asistencia técnica cotidiana, con roles y permisos diferenciados, borradores, publicación programada, vista previa y herramientas SEO.</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -757,7 +756,7 @@
           <t>Implementar las plantillas y componentes requeridos para home, categoría, artículo, autor, especiales, TV y Radio, así como cards, hero, breaking news, relacionados, citas destacadas, infografías y demás elementos editoriales definidos.</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -802,7 +801,7 @@
           <t>Implementar zonas publicitarias configurables en header, hero, grillas, sidebar y footer, con etiquetado visible, separación editorial, lazy loading y controles sobre la cantidad de anuncios visibles.</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -846,7 +845,7 @@
           <t>Implementar sitemap XML dinámico, URLs canónicas, breadcrumbs estructurados, Open Graph, Twitter Cards, RSS, preparación para Google News, metadatos y acciones orientadas a preservar el posicionamiento orgánico.</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -891,7 +890,7 @@
           <t>Ejecutar la migración del archivo histórico de CONtexto Ganadero, estimado en aproximadamente 41.000 artículos, incluyendo contenidos, imágenes, multimedia, autores, categorías, etiquetas, relaciones, fechas, URLs y metadatos, mediante procesos automatizados, trazables y verificables.</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -940,7 +939,7 @@
           <t>Ejecutar, conforme a la propuesta aceptada, la migración progresiva del archivo histórico por lotes durante tres meses, sin bloquear la salida a producción y validando cada lote antes de sustituir el contenido original.</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -983,7 +982,7 @@
           <t>Verificar la totalidad de contenidos migrados, integridad de campos y metadatos, URLs y redirecciones, indexación, enlaces internos, recursos multimedia, revisión editorial por muestreo y conciliación entre origen y destino.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1030,7 +1029,7 @@
           <t>Diseñar, desarrollar y validar el portal frente a las metas de rendimiento y Core Web Vitals definidas, incluyendo mediciones con Lighthouse, PageSpeed Insights, Search Console y, cuando aplique, Chrome UX Report.</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1077,7 +1076,7 @@
           <t>Implementar las medidas de seguridad, disponibilidad y observabilidad exigibles según el alcance contractual, incluyendo HTTPS, protección de formularios, buenas prácticas OWASP, autenticación segura, monitoreo y escalabilidad.</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1123,7 +1122,7 @@
           <t>Implementar las funcionalidades modernas que queden expresamente incluidas en el alcance contractual, tales como PWA, newsletter, (streaming ?, etiqueta En Vivo?, emisora? según la matriz definitiva de requerimientos aceptados) .</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1169,7 +1168,7 @@
           <t>Implementar Google Analytics 4, Google Tag Manager, Search Console y mecanismos de seguimiento editorial, técnico y de rendimiento, así como los tableros o reportes acordados.</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1214,7 +1213,7 @@
           <t>Implementar el asistente conversacional sobre el archivo histórico y los agentes de generación de borradores editoriales, con citación de fuentes y aprobación humana obligatoria antes de cualquier publicación.</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1259,7 +1258,7 @@
           <t>Aplicar reglas de gobernanza para IA que contemplen aprobación humana, trazabilidad, verificación de cifras, identificación del editor responsable, límites de uso y política institucional de utilización de IA.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1303,7 +1302,7 @@
           <t>Proveer y administrar durante la ejecución los ambientes de desarrollo, pruebas y producción, base de datos, almacenamiento, CDN, despliegue continuo y observabilidad, y transferir a FEDEGÁN las cuentas, credenciales y documentación correspondientes al cierre definido.</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1348,7 +1347,7 @@
           <t>Ejecutar pruebas técnicas, funcionales, editoriales, de rendimiento, seguridad y aceptación, asegurando el cumplimiento de los criterios definidos para arquitectura de información, home, categorías, artículos, móvil, publicidad, CMS, SEO, rendimiento y seguridad.</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1392,7 +1391,7 @@
           <t>Entregar documentación de base de datos, documentación técnica, manual editorial, manual de administración, credenciales y contraseñas, y realizar capacitación diferenciada para redactores, editores y administradores.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1437,7 +1436,7 @@
           <t>Entregar a FEDEGÁN el código fuente y la propiedad intelectual de la plataforma, junto con los elementos necesarios para su administración, mantenimiento y evolución posterior.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1482,7 +1481,7 @@
           <t>Cumplir los hitos, entregables y tiempos acordados contractualmente. Según la propuesta: salida a producción en la semana 6, estabilización durante dos meses, migración progresiva por tres meses y monitoreo posterior por seis meses.</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Cumplida</t>
         </is>
@@ -1607,7 +1606,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
@@ -1672,7 +1671,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -1682,7 +1681,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1722,7 +1721,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -630,6 +630,7 @@
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>• **Entregado el 18/10/2026: prototipos navegables E-02** (`docs/E-02-prototipos/index.html`, publicado como página privada): 12 pantallas del portal en producción (portada, sección, artículo, TV, Radio, Especiales, Regiones, Observatorio, buscador, asistente, boletín e ingreso al panel), en escritorio y celular, con notas de diseño y enlace a la página real.
+• Las 24 capturas (12 pantallas × escritorio y celular) también están en un archivo de Figma (imágenes, no capas editables) y en un PDF de entrega.
 • Sistema de diseño en código: 6 plantillas, tokens por plantilla, móvil primero, banco de pruebas responsive en Chrome real (17 tamaños).
 • Medido el 18/10/2026 con Lighthouse en producción: Accesibilidad 100, SEO 100 y Buenas prácticas 100 en sección, artículo, Observatorio y TV (el sitio actual: 86-96 de accesibilidad).</t>
         </is>
@@ -641,7 +642,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>E-02 (enlace a los prototipos navegables) para firma de FEDEGÁN.</t>
+          <t>E-02 (PDF de 14 páginas `docs/E-02_Prototipos_CONtexto_Ganadero.pdf`, enlace al visor navegable y archivo de Figma) para firma de FEDEGÁN.</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -993,7 +994,7 @@
       <c r="F14" s="3" t="inlineStr">
         <is>
           <t>• Herramienta de verificación hecha (`migracion:verificar`): conciliación completa origen-destino y muestra de URLs reales contra el sitio desplegado.
-• Comprobaciones hechas: 51.388 notas en los mapas del sitio, enlaces internos reescritos, redirecciones sobrantes limpiadas, 374 pruebas automáticas en verde.
+• Comprobaciones hechas: 51.388 notas en los mapas del sitio, enlaces internos reescritos, redirecciones sobrantes limpiadas, 375 pruebas automáticas en verde.
 • Búsqueda y listados probados con el volumen completo.</t>
         </is>
       </c>
@@ -1047,6 +1048,7 @@
       <c r="G15" s="3" t="inlineStr">
         <is>
           <t>• **La primera visita tras un rato sin tráfico (servidor en frío) supera la meta:** 2,8–3,4 s en portada, Colombia y TV. Las siguientes cumplen (1,45–1,9 s). Causa medida: la portada no queda guardada en la red de Vercel (cada respuesta llega `x-vercel-cache: MISS`), así que el primer visitante espera al servidor.
+• **Regiones (`/categoria/regiones?region=…`) sigue lenta en la primera visita:** medido en producción tras limitar el conteo, 4,1–6,6 s sin caché (antes ≈10–11 s); la meta fijada es 2,2 s. La corrección de fondo (región y departamento calculados por la base con índice) está construida y probada en local (migración 0023), pero NO está aplicada en producción ni medida: falta ejecutar `docs/supabase-zonas.sql` y publicar el código.
 • Corregir la caché de borde de la portada y las secciones y volver a medir.
 • Datos de campo (Search Console/CrUX) cuando haya tráfico; acordar con FEDEGÁN si la meta se mide en laboratorio o en campo.</t>
         </is>
@@ -1357,7 +1359,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>• **374 pruebas automáticas en verde** (permisos, 2FA, claves, límites, boletín, migración, búsqueda, «Más leídas», asistente, plantillas) con base PGlite en memoria; CI en cada cambio; banco responsive en Chrome real; mediciones de Lighthouse.</t>
+          <t>• **375 pruebas automáticas en verde** (permisos, 2FA, claves, límites, boletín, migración, búsqueda, «Más leídas», asistente, plantillas) con base PGlite en memoria; CI en cada cambio; banco responsive en Chrome real; mediciones de Lighthouse.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -1741,7 +1743,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>• 374 pruebas automáticas en verde.</t>
+          <t>• 375 pruebas automáticas en verde.</t>
         </is>
       </c>
     </row>

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>• `sitemap.xml` como índice (`/sitemaps/paginas.xml` + 6 archivos de notas): **51.388 notas en producción**; `news-sitemap.xml`, `robots.txt`, canónicas, NewsArticle y breadcrumbs JSON-LD, Open Graph, Twitter Cards, RSS (`/feed.xml`).
+          <t>• `sitemap.xml` como índice (`/sitemaps/paginas.xml` + 6 archivos de notas): **51.382 notas en producción**; `news-sitemap.xml`, `robots.txt`, canónicas, NewsArticle y breadcrumbs JSON-LD, Open Graph, Twitter Cards, RSS (`/feed.xml`).
 • Las direcciones de las notas antiguas se conservan exactamente (`legacy_path`), con 301 para las páginas institucionales y de columnistas del sitio anterior.</t>
         </is>
       </c>
@@ -901,7 +901,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>• **Migradas 51.388 notas a la base de producción** (el TDR estimaba ≈41.000): cuerpo, autor, categorías (y 4 nuevas: Galería, Video, Audio, Seguridad), etiquetas, fecha original, SEO, galerías, videos y audios.
+          <t>• **Migradas 51.382 notas a la base de producción** (el TDR estimaba ≈41.000): cuerpo, autor, categorías (y 4 nuevas: Galería, Video, Audio, Seguridad), etiquetas, fecha original, SEO, galerías, videos y audios.
 • Imágenes copiadas al almacenamiento propio (≈39.500 archivos, ≈9 GB, máx. 1.600 px): el sitio nuevo ya no depende de Storyblok.
 • Procesos automatizados y repetibles sin duplicar: `scripts/migracion/{descargar,cargar,verificar}.ts`; runbook en `docs/migracion-sitio-anterior.md` (51.527 de 51.535 direcciones descargadas; las 8 restantes dan 404/500 también en el sitio original).
 • Cada nota se sirve en su dirección original (sin redirección) y con canónica a sí misma.</t>
@@ -989,25 +989,27 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>• Herramienta de verificación hecha (`migracion:verificar`): conciliación completa origen-destino y muestra de URLs reales contra el sitio desplegado.
-• Comprobaciones hechas: 51.388 notas en los mapas del sitio, enlaces internos reescritos, redirecciones sobrantes limpiadas, 375 pruebas automáticas en verde.
-• Búsqueda y listados probados con el volumen completo.</t>
+          <t>• **Validación ejecutada el 19/10/2026** (informe `docs/validacion-migracion-2026-10-19.md`), sitio actual contra portal nuevo: 51.536 direcciones del sitio actual; las 51.535 notas responden; 51.381 migradas + 154 repetidas en dos secciones que redirigen a su copia (154 de 154 llegan a 200); 0 errores 404/500.
+• Muestreo de 150 notas al azar: titular y fecha idénticos en 150 de 150; 99,4 % de los párrafos del cuerpo presentes (143 de 150 notas completas).
+• Base de producción: 100 % con dirección original, categoría, autor, fecha y resumen; 0 portadas apuntando al servidor anterior.
+• Herramienta `migracion:verificar` y 375 pruebas automáticas en verde.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>• Ejecutar la verificación contra producción y archivar su informe (conciliación por sección, URLs, imágenes, enlaces rotos).
-• Revisión editorial por muestreo con una persona de la redacción (acta).
-• Medir cobertura de indexación en Search Console tras el corte de dominio.</t>
+          <t>• **438 notas con 535 imágenes dentro del texto que siguen en el servidor del sitio anterior** (y 99 con enlaces): se romperán al cancelarlo; hay que repetir el paso de imágenes para esas notas.
+• 7.391 notas (14 %) con título SEO distinto del titular que mostraba el sitio actual: decisión de FEDEGÁN.
+• 2.911 notas sin imagen de portada (confirmar que ya carecían de ella) y 7 notas de la muestra con un párrafo distinto.
+• Revisión editorial por muestreo con una persona de la redacción (acta) y cobertura de indexación en Search Console tras el corte de dominio.</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Informe de conciliación y validación (salida de `migracion:verificar` + acta del muestreo editorial).</t>
+          <t>Informe de validación `docs/validacion-migracion-2026-10-19.md` + acta del muestreo editorial.</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -1723,7 +1725,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="10">
@@ -1736,7 +1738,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>• Migración completada: 51.388 notas en producción (estimado TDR ≈41.000).</t>
+          <t>• Migración completada: 51.382 notas en producción (estimado TDR ≈41.000).</t>
         </is>
       </c>
     </row>

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -1001,9 +1001,9 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>• **438 notas con 535 imágenes dentro del texto que siguen en el servidor del sitio anterior** (y 99 con enlaces): se romperán al cancelarlo; hay que repetir el paso de imágenes para esas notas.
-• 7.391 notas (14 %) con título SEO distinto del titular que mostraba el sitio actual: decisión de FEDEGÁN.
-• 2.911 notas sin imagen de portada (confirmar que ya carecían de ella) y 7 notas de la muestra con un párrafo distinto.
+          <t>• **438 notas con 535 imágenes dentro del texto que siguen en el servidor del sitio anterior** (y 99 con enlaces): se romperán al cancelarlo. Storyblok hoy responde 403 a esas imágenes, así que no se pudieron copiar; script `reparar-imagenes.ts` listo para repetir la copia cuando respondan (no cancelar el sitio anterior antes).
+• 7.391 notas (14 %) con título SEO distinto del titular que mostraba el sitio actual: respaldo y SQL listos (`docs/sql-titulo-seo.sql`), falta ejecutarlo y la decisión de FEDEGÁN.
+• 2.911 notas sin portada: 2.670 son columnas (el sitio actual usa el logo); las otras 241 se recuperan con el script cuando Storyblok responda. Las «7 notas con un párrafo distinto» eran texto ajeno a la nota (falso positivo).
 • Revisión editorial por muestreo con una persona de la redacción (acta) y cobertura de indexación en Search Console tras el corte de dominio.</t>
         </is>
       </c>

--- a/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
+++ b/docs/Obligaciones_Contratista_Estado_2026-10-18.xlsx
@@ -1401,28 +1401,29 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>• Documentación: arquitectura, base de datos (generada), manual editorial, manual de administración, seguridad, migración, consejo de redacción, medición de rendimiento y guía técnica del CMS.</t>
+          <t>• **Paquete de 9 documentos controlados emitido el 19/10/2026** (`docs/obligacion-19/`, PDF con huellas SHA-256): índice y trazabilidad (CG-DOC-00), documentación técnica (01), documentación de la base de datos con diccionario de las 26 tablas y volúmenes reales de producción (02), manual editorial (03), manual de administración (04), seguridad con matriz de 39 controles y su evidencia (05), operación, continuidad y recuperación con 12 procedimientos (06), inventario de cuentas y credenciales con acta de entrega firmable (07) y plan de capacitación diferenciada con guías rápidas, ejercicios y formatos de asistencia y evaluación (08).
+• Manuales actualizados con lo construido desde el 6/10: editor de portada, newsletter por pasos, consejo de redacción (temas, tareas del equipo, mis pendientes, escribir una tarea), «Más leídas», panel por plantilla.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>• Actualizar los manuales con lo construido desde el 6/10 (editor de portada, newsletter por pasos, consejo de redacción, «Más leídas», panel por plantilla).
-• Capacitación diferenciada (redactores, editores, administradores): sesiones y grabaciones.
-• Entrega formal de credenciales y contraseñas.</t>
+          <t>• **Entrega efectiva de credenciales y contraseñas:** exige a FEDEGÁN la bóveda, dos custodios y la transferencia de titularidad de Vercel, Supabase y GitHub; después el contratista rota los secretos y se firma el acta (CG-DOC-07).
+• **Dictar las tres capacitaciones** (redactores, editores y administradores) y firmar los registros de asistencia, evaluación y acta (CG-DOC-08).
+• Aprobación de los documentos por FEDEGÁN y confirmación de los puntos «a confirmar» (plan de Vercel y Supabase, reglas del Firewall, política de respaldos). Hallazgo abierto H-D1: cifrar el secreto TOTP de `users`.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Manuales actualizados + plan y registro de capacitación + acta de entrega de credenciales.</t>
+          <t>Paquete `Obligacion_19_Documentacion` (9 PDF + huellas) + actas firmadas de capacitación y de entrega de credenciales.</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Contratista</t>
+          <t>Contratista + FEDEGÁN</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1726,7 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="10">
